--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>9/29/2026, 1:14:13 PM</v>
+        <v>9/29/2026, 1:25:59 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>9/29/2026, 1:25:59 PM</v>
+        <v>9/30/2026, 5:52:26 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>9/30/2026, 5:52:26 PM</v>
+        <v>10/1/2026, 12:06:17 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/1/2026, 12:06:17 PM</v>
+        <v>10/1/2026, 12:21:14 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/1/2026, 12:21:14 PM</v>
+        <v>10/1/2026, 12:25:57 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/1/2026, 12:25:57 PM</v>
+        <v>10/1/2026, 1:31:38 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/1/2026, 1:31:38 PM</v>
+        <v>10/1/2026, 1:51:28 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/1/2026, 1:51:28 PM</v>
+        <v>10/2/2026, 7:42:26 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/2/2026, 7:42:26 PM</v>
+        <v>10/2/2026, 9:01:16 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/2/2026, 9:01:16 PM</v>
+        <v>10/2/2026, 9:02:40 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/2/2026, 9:02:40 PM</v>
+        <v>10/3/2026, 9:55:28 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/3/2026, 9:55:28 PM</v>
+        <v>10/3/2026, 9:57:13 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/3/2026, 9:57:13 PM</v>
+        <v>10/4/2026, 1:01:57 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/4/2026, 1:01:57 PM</v>
+        <v>10/16/2026, 12:48:27 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/16/2026, 12:48:27 PM</v>
+        <v>10/17/2026, 6:07:18 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/17/2026, 6:07:18 PM</v>
+        <v>10/19/2026, 2:01:00 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3855,7 +3855,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>10/19/2026, 2:01:00 PM</v>
+        <v>10/19/2026, 2:08:50 PM</v>
       </c>
     </row>
   </sheetData>
